--- a/www/download/COUNTRY.AUT.WIOD13.xlsx
+++ b/www/download/COUNTRY.AUT.WIOD13.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Áustria</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.731818001159724</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>0.769047362910261</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>0.885708209560329</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>0.89831921167159</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>0.938262383745538</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>1.08271976620737</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>1.11656987330822</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>1.05752964594517</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>0.884017009908191</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.803923182414509</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>0.803793923570613</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>0.796432004858313</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>0.729660722254592</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.679902074833737</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.71694869546993</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.717</t>
+          <t>-0.36697142435328</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.746</t>
+          <t>-0.342786052328007</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3.773</t>
+          <t>-0.206906613298569</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3.813</t>
+          <t>-0.209543224006525</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.881</t>
+          <t>-0.216008556679436</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.931</t>
+          <t>-0.149868284622965</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.959</t>
+          <t>-0.150588501749006</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.959</t>
+          <t>-0.157394699900883</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>3.971</t>
+          <t>-0.191960899746963</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>3.986</t>
+          <t>-0.246880031357208</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>4.031</t>
+          <t>-0.256673288442381</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>-0.275511282792211</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>4.161</t>
+          <t>-0.277429699185534</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>-0.260057715624549</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>4.213</t>
+          <t>-0.200170697315601</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.126</t>
+          <t>0.0567310662891023</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.123</t>
+          <t>0.102443709161079</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3.151</t>
+          <t>0.296934163903501</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3.184</t>
+          <t>0.277028924183672</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3.239</t>
+          <t>0.259427206301593</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.278</t>
+          <t>0.339029281863222</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>0.325630445508075</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.293</t>
+          <t>0.324414309276383</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>3.302</t>
+          <t>0.265097656861603</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>3.315</t>
+          <t>0.202879587830145</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>3.353</t>
+          <t>0.180310005716608</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>3.408</t>
+          <t>0.162210984513704</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>0.160163818636401</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>3.569</t>
+          <t>0.214390888563969</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>3.543</t>
+          <t>0.310793460583662</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>6149.242</t>
+          <t>0.541593550602879</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6212.278</t>
+          <t>0.610840738484212</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6288.025</t>
+          <t>0.896193443143876</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>6361.278</t>
+          <t>0.888676804643634</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6424.814</t>
+          <t>0.847534981339543</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6518.098</t>
+          <t>0.957183203738011</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6559.398</t>
+          <t>0.948811405729612</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>6542.049</t>
+          <t>0.930444933138143</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>6583.091</t>
+          <t>0.383234364922211</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>6630.014</t>
+          <t>0.699247820131132</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>6658.907</t>
+          <t>0.683892542027002</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>6717.025</t>
+          <t>0.683702229827612</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>6788.639</t>
+          <t>0.798714489020917</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>6968.04</t>
+          <t>0.965095293963422</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>6613.166</t>
+          <t>1.1190524389081</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4827.845</t>
+          <t>9344869532.70493</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4833.915</t>
+          <t>9602711997.42938</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4916.552</t>
+          <t>8974195730.38566</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>4991.233</t>
+          <t>9189504293.40765</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>5053.095</t>
+          <t>9325806863.85815</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5121.332</t>
+          <t>9670505207.67163</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5161.275</t>
+          <t>9819235686.09696</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>5133.78</t>
+          <t>9557294113.069</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>5169.977</t>
+          <t>9885308499.40412</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>5204.784</t>
+          <t>10211180026.5304</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>5217.574</t>
+          <t>10072141962.724</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>5277.349</t>
+          <t>10857947449.4273</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>5371.388</t>
+          <t>11163869261.795</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>5486.016</t>
+          <t>10292353238.1873</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>5327.349</t>
+          <t>8798815535.73075</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>4671997960.05508</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>4509000928.97057</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>16.79</t>
+          <t>3890272592.23915</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>4006679804.8301</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4154686202.73968</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>20.27</t>
+          <t>3960407923.74285</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20.28</t>
+          <t>4038222056.20934</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>20.74</t>
+          <t>4041676557.09405</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>19.59</t>
+          <t>4416213756.04254</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>24.92</t>
+          <t>4628200675.86006</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>24.02</t>
+          <t>4702135967.26963</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>4818411710.20289</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>4871510841.31536</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>4775598715.59118</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>25.04</t>
+          <t>4334722559.95287</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>999122.899954517</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>68.05</t>
+          <t>1065198.23579569</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>68.62</t>
+          <t>1088804.29647708</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>68.52</t>
+          <t>1107493.37981094</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>65.65</t>
+          <t>1161364.30615776</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>65.53</t>
+          <t>1305617.84261956</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>66.18</t>
+          <t>1296974.19821357</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>66.11</t>
+          <t>1180008.32452639</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>63.58</t>
+          <t>997741.792164231</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>63.14</t>
+          <t>894626.613179597</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>64.33</t>
+          <t>846902.900780348</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>830011.889105936</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>63.94</t>
+          <t>721615.798182533</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>65.14</t>
+          <t>569839.811784431</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>64.9</t>
+          <t>562242.070681744</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>26993.1999650274</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>15.09</t>
+          <t>27103.4411898283</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>14.59</t>
+          <t>27069.6449391828</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>14.68</t>
+          <t>26910.9848960791</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>27340.9534733306</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>28555.8429119741</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>13.54</t>
+          <t>27796.4084419178</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>13.15</t>
+          <t>28105.3823790047</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>16.83</t>
+          <t>30365.2368507588</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>11.94</t>
+          <t>33549.1139937556</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>11.65</t>
+          <t>35369.6310782755</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>12.17</t>
+          <t>37004.8727365691</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>42083.7094437645</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>11.05</t>
+          <t>47572.4284245116</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>41419.1397864515</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>11.31</t>
+          <t>72752.3610298521</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>11.31</t>
+          <t>75315.5571608565</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11.37</t>
+          <t>69933.9870213347</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>71219.009978881</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>73844.7661572102</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>13.97</t>
+          <t>79673.0520424066</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>78778.553662458</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>14.42</t>
+          <t>78387.7341993598</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>14.32</t>
+          <t>87333.6896260929</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>17.46</t>
+          <t>99419.0118698319</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>16.89</t>
+          <t>105027.568352207</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>118663.178474376</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>138025.875617739</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>16.39</t>
+          <t>140880.907593321</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>112342.394944382</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>66.74</t>
+          <t>0.033357685786122</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>67.97</t>
+          <t>0.0720589940316576</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>68.69</t>
+          <t>0.263806554278025</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>68.24</t>
+          <t>0.245727945113809</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>66.21</t>
+          <t>0.216239868288463</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>66.18</t>
+          <t>0.293132449639178</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>66.86</t>
+          <t>0.278105792142808</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>66.95</t>
+          <t>0.270210499894918</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>67.04</t>
+          <t>0.170680878597897</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>65.46</t>
+          <t>0.124580450270297</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>66.46</t>
+          <t>0.109617849487596</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>66.07</t>
+          <t>0.0952465910759184</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>65.1</t>
+          <t>0.102612346552772</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>66.24</t>
+          <t>0.14875983656028</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>66.52</t>
+          <t>0.228994226578118</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>21.94</t>
+          <t>59905.1944367106</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>20.73</t>
+          <t>58979.3238179988</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>19.94</t>
+          <t>52914.4784816549</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>53734.4415345215</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20.16</t>
+          <t>49279.8111499762</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>46677.1786338813</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>46164.5574335721</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>18.64</t>
+          <t>48650.1992998487</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>18.64</t>
+          <t>58397.3686997921</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>65966.6454507814</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>67161.0479808406</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>17.43</t>
+          <t>69305.3735133582</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>18.12</t>
+          <t>76423.5171545305</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>17.37</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>15.93</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.731818001159724</t>
+          <t>1494.47790175949</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.769047362910261</t>
+          <t>1443.99298050164</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.885708209560329</t>
+          <t>1234.79314132825</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.89831921167159</t>
+          <t>1258.18215199003</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.938262383745538</t>
+          <t>1282.72150236393</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.08271976620737</t>
+          <t>1208.31046589387</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.11656987330822</t>
+          <t>1223.63097713267</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.05752964594517</t>
+          <t>1227.52206788541</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.884017009908191</t>
+          <t>1337.49556871325</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.803923182414509</t>
+          <t>1396.15412893173</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.803793923570613</t>
+          <t>1402.50569614099</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.796432004858313</t>
+          <t>1414.04323415614</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.729660722254592</t>
+          <t>1400.05214548651</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.679902074833737</t>
+          <t>1337.97293951837</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.71694869546993</t>
+          <t>1223.45070743202</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>2923580129.11993</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>2843769210.7109</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>2618395021.38542</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>3145926013.11581</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>3587663139.24422</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>3649693774.51153</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>4068286068.69066</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>4720923913.50698</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>5081317840.78742</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>5724559465.69697</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>5999797654.61642</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>6691391026.80324</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>7046824338.18335</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>7167399787.77784</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>6102646840.27469</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>2794326216.1941</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>2806252611.77516</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>2535511664.88559</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>2929100845.04391</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>3167677863.81788</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>3205592158.56776</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>3487782758.68861</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>4102587247.47369</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>4423123950.70127</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>4974759656.22878</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>5040924711.67782</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>5506661251.22799</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>5824715524.24624</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.244</t>
+          <t>5870107032.30499</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.231</t>
+          <t>4938666922.30997</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.858</t>
+          <t>129253912.925826</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.847</t>
+          <t>37516598.9357461</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.763</t>
+          <t>82883356.4998248</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.771</t>
+          <t>216825168.071898</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.752</t>
+          <t>419985275.426345</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.681</t>
+          <t>444101615.94377</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.676</t>
+          <t>580503310.002051</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.729</t>
+          <t>618336666.033289</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.888</t>
+          <t>658193890.086152</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>749799809.46819</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1.027</t>
+          <t>958872942.938601</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>1.071</t>
+          <t>1184729775.57525</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>1.216</t>
+          <t>1222108813.93711</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1297292755.47286</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1163979917.96472</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.396</t>
+          <t>1544.33022602069</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.389</t>
+          <t>1548.04566206536</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>1560.53966518819</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>1567.35266677741</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.358</t>
+          <t>1560.09703108588</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>1562.505472686</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>1563.92983931863</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.366</t>
+          <t>1559.21141948077</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.451</t>
+          <t>1565.78048750202</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.524</t>
+          <t>1570.08763896079</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.557</t>
+          <t>1556.24535444607</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.606</t>
+          <t>1548.72603184348</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.704</t>
+          <t>1543.71478143112</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.799</t>
+          <t>1537.0095753232</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.719</t>
+          <t>1503.61385593687</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>1654.15594022784</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>1658.55040317898</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>1666.47452461406</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>1668.39714981714</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>1655.63795187662</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>1658.07151731359</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>1656.83956128116</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>1652.24286121264</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>1657.70574480397</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.261</t>
+          <t>1663.32263423587</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>1651.80468197293</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>1642.10847214318</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>1631.54473131314</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.374</t>
+          <t>1620.40036553057</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.343</t>
+          <t>1569.76117101912</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-36.7</t>
+          <t>70221.1915103936</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-34.28</t>
+          <t>71629.4205159264</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>-20.69</t>
+          <t>71205.5404294847</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-20.95</t>
+          <t>77143.1228463394</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-20.61</t>
+          <t>78761.5458660388</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-14.99</t>
+          <t>78442.822771672</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-15.06</t>
+          <t>82279.5699330537</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-15.75</t>
+          <t>90534.7975304621</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-19.21</t>
+          <t>109342.604936076</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-24.69</t>
+          <t>132051.931142555</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-25.67</t>
+          <t>144305.812951195</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>-27.55</t>
+          <t>162637.198567264</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>-27.76</t>
+          <t>194688.095693501</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>-26.01</t>
+          <t>218578.155408561</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>-20.02</t>
+          <t>168010.107892263</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>1975747017.83143</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>10.25</t>
+          <t>2106941858.31925</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>29.69</t>
+          <t>2199602511.76685</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>27.72</t>
+          <t>2433696786.84041</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>2566610846.49469</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>33.9</t>
+          <t>2823014713.3978</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>32.57</t>
+          <t>2982981198.32516</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>32.42</t>
+          <t>2987772442.24134</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>3114045428.00016</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>20.28</t>
+          <t>3446188488.04961</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>18.03</t>
+          <t>3509552136.4422</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>16.22</t>
+          <t>3886790367.97449</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>4159214513.07913</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>21.43</t>
+          <t>3890567394.54306</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>31.08</t>
+          <t>2924842861.91623</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>75260.6971182159</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>61.09</t>
+          <t>77186.7495395973</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>89.62</t>
+          <t>73026.5198838892</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>88.89</t>
+          <t>76640.2749238926</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>87.09</t>
+          <t>77362.0404008275</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>95.71</t>
+          <t>75856.154195472</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>94.89</t>
+          <t>78919.8362097961</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>93.02</t>
+          <t>82047.7350665363</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>101992.001705655</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>69.92</t>
+          <t>122693.660633994</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>68.39</t>
+          <t>133793.876633681</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>68.37</t>
+          <t>147182.496457625</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>79.83</t>
+          <t>174264.314043969</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>197448.313223165</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>111.9</t>
+          <t>153419.230800393</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>6149.242</t>
+          <t>5677418222.91091</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>6212.278</t>
+          <t>5774393464.61236</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>6288.025</t>
+          <t>5067183544.31751</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>6361.278</t>
+          <t>5507183801.79023</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>6424.814</t>
+          <t>5943801487.60769</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6518.098</t>
+          <t>6088722643.13466</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>6559.398</t>
+          <t>6526887865.66084</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>6542.049</t>
+          <t>6398922199.12183</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>6583.091</t>
+          <t>7124993291.0543</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>6630.014</t>
+          <t>7921041067.47309</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>6658.907</t>
+          <t>8208218779.27884</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>6717.025</t>
+          <t>8833272966.95197</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>6788.639</t>
+          <t>9173183551.53809</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>6968.04</t>
+          <t>9196371903.95498</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>6613.166</t>
+          <t>7613920845.95947</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>4827.845</t>
+          <t>-5039.50560782232</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4833.915</t>
+          <t>-5557.3290236709</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>4916.552</t>
+          <t>-1820.97945440447</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>4991.233</t>
+          <t>502.847922446811</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>5053.095</t>
+          <t>1399.50546521129</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>5121.332</t>
+          <t>2586.66857619994</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5161.275</t>
+          <t>3359.73372325755</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>5133.78</t>
+          <t>8487.06246392574</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>5169.977</t>
+          <t>7350.60323042168</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>5204.784</t>
+          <t>9358.27050856001</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>5217.574</t>
+          <t>10511.9363175145</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>5277.349</t>
+          <t>15454.7021096393</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>5371.388</t>
+          <t>20423.7816495321</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>5486.016</t>
+          <t>21129.8421853959</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>5327.349</t>
+          <t>14590.8770918695</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>9345.724</t>
+          <t>-3701671205.07948</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>9601.809</t>
+          <t>-3667451606.29311</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>8974.217</t>
+          <t>-2867581032.55066</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>9188.01</t>
+          <t>-3073487014.94983</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>9232.266</t>
+          <t>-3377190641.113</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>9670.591</t>
+          <t>-3265707929.73686</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>9818.732</t>
+          <t>-3543906667.33568</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>9558.109</t>
+          <t>-3411149756.88049</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>9886.48</t>
+          <t>-4010947863.05414</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>10212.736</t>
+          <t>-4474852579.42348</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>10072.033</t>
+          <t>-4698666642.83665</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>10858.162</t>
+          <t>-4946482598.97748</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>11168.639</t>
+          <t>-5013969038.45896</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>10293.085</t>
+          <t>-5305804509.41192</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>8799.273</t>
+          <t>-4689077984.04324</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>104760.33174</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>101689.78559</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>89378.24209</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>91381.75096</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>90242.02239</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>81672.55084</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>80967.34353</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>86866.56089</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>106169.29782</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>120195.45537</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>122775.57934</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>131589.88057</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>153572.69415</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>167643.75389</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>150659.26576</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>3467.213</t>
+          <t>0.00607600411183725</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>3455.681</t>
+          <t>0.00576658711067155</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3473.68</t>
+          <t>0.00592240140893155</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>3472.368</t>
+          <t>0.00754953519224756</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>3452.871</t>
+          <t>0.0126022274768346</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>3466.033</t>
+          <t>0.0124289693048915</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3464.642</t>
+          <t>0.015053634070382</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>3426.702</t>
+          <t>0.0187759480420168</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>3437.044</t>
+          <t>0.0200002274892132</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>3445.78</t>
+          <t>0.0240872264300253</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>3391.947</t>
+          <t>0.027270193743673</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>3386.029</t>
+          <t>0.0325010194443578</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>3403.833</t>
+          <t>0.0380074899907183</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>3475.505</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>3244.006</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>127992.186669422</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>123152.953138419</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>108742.303558698</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>111117.858937595</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>110147.54241072</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>98683.3827996589</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>97497.3858792404</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>104707.904963036</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>127950.733972506</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>143456.680272801</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>148695.16079702</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>157113.790745812</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>180261.99366911</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>204525.199765735</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>194288.149892041</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>4672.373</t>
+          <t>149675.606169677</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>4508.849</t>
+          <t>145738.318632223</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3890.283</t>
+          <t>128695.957262441</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>4006.234</t>
+          <t>131521.983285444</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>4102.715</t>
+          <t>130408.256575546</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>3960.6</t>
+          <t>117186.843937276</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>4038.075</t>
+          <t>115641.130433391</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>4042.248</t>
+          <t>124600.275081746</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>4416.84</t>
+          <t>152362.597063906</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>4628.32</t>
+          <t>171096.132710131</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>4702.023</t>
+          <t>177805.570901088</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>4818.522</t>
+          <t>187820.15928529</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>4872.564</t>
+          <t>214640.180802592</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>4775.814</t>
+          <t>244328.853363102</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>4334.862</t>
+          <t>230988.738402635</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>858090.456761757</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>7.21</t>
+          <t>847096.229715934</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>26.38</t>
+          <t>762889.330515573</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>24.59</t>
+          <t>771212.170255622</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>23.16</t>
+          <t>752101.804375487</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>29.31</t>
+          <t>681310.690461719</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>676495.154287948</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>728771.629948285</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>888093.606229298</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>1000256.00286859</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>10.96</t>
+          <t>1027107.91024614</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>1071058.63251297</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>1216284.32354166</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>14.87</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.999</t>
+          <t>149675.606169677</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.065</t>
+          <t>152691.030601402</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.089</t>
+          <t>157461.764726779</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1.107</t>
+          <t>162094.160196009</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.148</t>
+          <t>167394.104954669</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.306</t>
+          <t>170521.354659441</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.297</t>
+          <t>168774.187723964</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>170009.417192656</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.998</t>
+          <t>171811.297939903</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.895</t>
+          <t>174068.002670102</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.847</t>
+          <t>178699.732476272</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>183093.249167409</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.722</t>
+          <t>187721.335010179</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>196992.289731559</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.562</t>
+          <t>195767.940267466</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>127992.186669422</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>128756.933028637</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>133075.529494262</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>136679.262918424</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>141067.32458586</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>143759.007506718</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>142870.808695962</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>143608.416383328</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>144896.61670163</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>146330.37516427</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>149204.514366132</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>153538.354664414</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>158419.075301162</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>165301.617470886</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>164891.916656432</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>65118.9555803234</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>63864.1780177772</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>57432.6153275592</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>59556.7349545559</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>58757.9691744538</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>55145.1682927244</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>56348.2679366094</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>62333.5775582536</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>76159.4428560938</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>90060.0382798691</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>95170.4796889121</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>104115.87095471</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>122651.431407408</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>129268.073736898</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>112211.002247365</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>4827845000</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>4833915000</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>4916552000</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>4991233000</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>5053095000</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>5121332000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>5161275000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>5133780000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>5169977000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>5204784000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>5217574000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>5277349000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>5371388000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>5486016000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>5327349000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>6149242000</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>6212278000</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>6288025000</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>6361278000</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>6424814000</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>6518098000</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>6559398000</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>6542049000</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>6583091000</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>6630014000</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>6658907000</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>6717025000</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>6788639000</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>6968039603.14124</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>6613166129.92754</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>3467213000</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>3455681000</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>3473680000</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>3472368000</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>3452871000</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>3466033000</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3464642000</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>3426702000</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>3437044000</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>3445780000</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>3391947000</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>3386029000</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>3403833000</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>3475504566.99832</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>3244005709.59928</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>3717450</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>3745607</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>3773250</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>3812808</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>3880567</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>3931132</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>3958982</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>3959496</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>3971206</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>3986006</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>4031292</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>4090488</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>4160866</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>4300196.26714888</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>4212848.58615411</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>3126174</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>3122592</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>3150546</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>3184499</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>3238962</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>3277641</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3300196</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>3292549</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>3301853</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>3314964</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>3352668</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>3407542</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>3479521</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>3569279</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>3543030</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>6149242000</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>6212278000</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>6288025000</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>6361278000</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>6424814000</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>6518098000</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>6559398000</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>6542049000</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>6583091000</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>6630014000</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>6658907000</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>6717025000</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>6788639000</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>6968039603.14124</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>6613166129.92754</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>4827845000</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>4833915000</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>4916552000</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>4991233000</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>5053095000</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>5121332000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5161275000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>5133780000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>5169977000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>5204784000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>5217574000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>5277349000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>5371388000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>5486016000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>5327349000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.169044817094115</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.168630359599756</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.167903365965459</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.168023523377907</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.199963111373848</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.202676400790775</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.202802552594371</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.207401147367655</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.195924358814711</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.24918943413737</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.240157875391057</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.235950322844061</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.240306739208807</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.238106026799351</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.250441977970516</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.671010166280092</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.680511013366372</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.686200441353039</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.685156538978708</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.656510514138975</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.655278617902113</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.661846026462975</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.661078921494902</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.63577070785497</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.63137656510983</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.643327008916173</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.64238490261995</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.639442539353564</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.651407027183705</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.649049853514358</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.159945016625794</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.150858627033873</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.145896192681503</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.146819937643385</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.143526374487177</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.142044981307112</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.135351420942655</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.131519931137443</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.168304933330319</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.1194340007528</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.11651511569277</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.121664774535988</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.120250721437629</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.110486946016944</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.100508168515127</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.113137247731648</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.1130773975395</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.113718272828169</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.11418334035063</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.136361356854577</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.139704039706494</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.140254486022889</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.144158214523391</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.143225011137814</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.174623171220739</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.168877336334161</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.164995263524689</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.167797619169898</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.163870769885039</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.175496739843436</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.667441399753227</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.67965633652255</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.686852596963825</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.682352512144294</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.662085467053103</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.661808110937379</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.668640698699335</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.669477251930921</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.67036171385888</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.654647805504798</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.664638824404813</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.660742385300573</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.65102115522402</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.662419824639012</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.665221646858623</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.219421352515125</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.207266265937951</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.199429130208006</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.203464147505076</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.20155317609232</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.198487849356127</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.191104815277776</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.186364533545689</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.186413275003306</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.170729023274463</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.166483839261025</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.174262351174738</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.181181225606082</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.173709405475949</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.159281613297941</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>396167.78119</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>389425.34302</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>349702.38207</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>359863.73897</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>357693.89626</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>331113.21482</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>336888.92575</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>365545.88064</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>451468.87916</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>523577.54357</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>556508.18899</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>605744.10582</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>704248.97568</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>799375.40736</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>719449.87965</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>214794.56175</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>209602.49665</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>186128.57259</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>191078.71824</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>189166.22575</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>172332.01223</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>171989.39837</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>186933.85264</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>228522.03992</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>261156.17099</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>272976.05059</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>291936.03024</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>337291.61221</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>373596.9271</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>343199.74065</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>627966.047148864</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>643018.446992757</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>658133.880369315</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>674449.139747487</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>691479.658955472</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>710332.219848021</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>728424.579828148</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>742944.45226883</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>759153.168849483</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>774058.063538429</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>789134.284570129</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>806369.874104814</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>825345.996961871</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD13</t>
